--- a/artfynd/A 11233-2025 artfynd.xlsx
+++ b/artfynd/A 11233-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15595343</v>
+        <v>13546532</v>
       </c>
       <c r="B2" t="n">
-        <v>42719</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -723,19 +718,24 @@
           <t>friflygande</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grindugastigen 3, Gstr</t>
+          <t>Horsåker, vid Älgsjöbäcken, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625041.5321948121</v>
+        <v>624961</v>
       </c>
       <c r="R2" t="n">
-        <v>6723253.085160797</v>
+        <v>6723262</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-07-21</t>
+          <t>2008-07-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-07-21</t>
+          <t>2008-07-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,53 +789,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Sjödin</t>
+          <t>Oskar Kindvall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Björn Sjödin</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Faunaväkteri småkryp</t>
-        </is>
-      </c>
+          <t>Oskar Kindvall, olle kindvall</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54468428</v>
+        <v>13546528</v>
       </c>
       <c r="B3" t="n">
-        <v>42621</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>201122</v>
+        <v>201075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Almsnabbvinge</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Satyrium w-album</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Knoch, 1782)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,16 +834,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -862,17 +851,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grindugastigen 3, Gstr</t>
+          <t>Horsåker, vid Älgsjöbäcken, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625041.5321948121</v>
+        <v>624961</v>
       </c>
       <c r="R3" t="n">
-        <v>6723253.085160797</v>
+        <v>6723262</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,22 +885,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
+          <t>2008-07-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
+          <t>2008-07-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,49 +915,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Björn Sjödin</t>
+          <t>Oskar Kindvall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Björn Sjödin</t>
+          <t>Oskar Kindvall, olle kindvall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60729033</v>
+        <v>13546479</v>
       </c>
       <c r="B4" t="n">
-        <v>44330</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102018</v>
+        <v>201146</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -976,16 +960,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -995,17 +982,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grindugastigen 3, Gstr</t>
+          <t>Horsåker, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625041.5321948121</v>
+        <v>625071</v>
       </c>
       <c r="R4" t="n">
-        <v>6723253.085160797</v>
+        <v>6723294</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,22 +1016,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-07-27</t>
+          <t>2008-07-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-07-27</t>
+          <t>2008-07-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,66 +1046,59 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Björn Sjödin</t>
+          <t>Oskar Kindvall</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Björn Sjödin</t>
+          <t>Oskar Kindvall, olle kindvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>60729042</v>
+        <v>13546517</v>
       </c>
       <c r="B5" t="n">
-        <v>44332</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102020</v>
+        <v>201146</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1128,17 +1108,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grindugastigen 3, Gstr</t>
+          <t>Horsåker, vid Älgsjöbäcken, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625041.5321948121</v>
+        <v>624961</v>
       </c>
       <c r="R5" t="n">
-        <v>6723253.085160797</v>
+        <v>6723262</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1162,22 +1142,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-07-27</t>
+          <t>2008-07-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-07-27</t>
+          <t>2008-07-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1192,27 +1172,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Björn Sjödin</t>
+          <t>Oskar Kindvall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Björn Sjödin</t>
+          <t>Oskar Kindvall, olle kindvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113529680</v>
+        <v>68512068</v>
       </c>
       <c r="B6" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,37 +1195,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gävle_Älvkarleby, Gstr</t>
+          <t>Älgsjöbäcken, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625088</v>
+        <v>624973</v>
       </c>
       <c r="R6" t="n">
-        <v>6723202</v>
+        <v>6723207</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,17 +1249,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2017-09-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Calluna_AB</t>
+          <t>2017-09-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,23 +1265,455 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>50-årig, planterad granskog med lågört</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129418465</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grinduga SO ca 1200 m, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>624917</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6723344</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Bergvik skog öst</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>trolig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>trädformig</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>68512071</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Älgsjöbäcken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>624995</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6723237</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>50-årig, planterad granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113529680</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gävle_Älvkarleby, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>625088</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6723202</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Calluna_AB</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Tom Brodin</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Tom Brodin, Milad Avalinejad Bandari</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>AKE0012 Kompletterande NVI del 2</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>68512069</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Älgsjöbäcken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>624971</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6723211</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>50-årig, planterad granskog med lågört</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11233-2025 artfynd.xlsx
+++ b/artfynd/A 11233-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13546532</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13546528</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1055,6 +1070,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13546479</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1181,6 +1201,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13546517</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1283,6 +1308,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68512068</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1395,6 +1425,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129418465</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68512071</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1612,6 +1652,11 @@
           <t>AKE0012 Kompletterande NVI del 2</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113529680</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1714,8 +1759,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68512069</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>